--- a/diagtab/demo/demo_diagtab.xlsx
+++ b/diagtab/demo/demo_diagtab.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="228" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" count="228" uniqueCount="89">
   <si>
     <t>Low birth weight prediction</t>
   </si>
@@ -144,6 +144,9 @@
   </si>
   <si>
     <t>Predictive values at 7% prevalence</t>
+  </si>
+  <si>
+    <t>Accuracy (sample)</t>
   </si>
   <si>
     <t>10.9%</t>
@@ -909,10 +912,10 @@
         <v>7</v>
       </c>
       <c r="C9" s="15" t="s">
-        <v>43</v>
+        <v>44</v>
       </c>
       <c r="D9" s="15" t="s">
-        <v>45</v>
+        <v>46</v>
       </c>
     </row>
     <row r="10">
@@ -923,10 +926,10 @@
         <v>8</v>
       </c>
       <c r="C10" s="15" t="s">
-        <v>44</v>
+        <v>45</v>
       </c>
       <c r="D10" s="15" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="11">
@@ -934,7 +937,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>9</v>
+        <v>43</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>23</v>
@@ -1019,7 +1022,7 @@
   <sheetData>
     <row r="1">
       <c r="A1" s="20" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>1</v>
@@ -1036,7 +1039,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="27" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="C2" s="27" t="s">
         <v>18</v>
@@ -1050,7 +1053,7 @@
         <v>1</v>
       </c>
       <c r="B3" s="21" t="s">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="C3" s="21" t="s">
         <v>1</v>
@@ -1064,13 +1067,13 @@
         <v>1</v>
       </c>
       <c r="B4" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C4" s="15" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="D4" s="15" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
     </row>
     <row r="5">
@@ -1078,13 +1081,13 @@
         <v>1</v>
       </c>
       <c r="B5" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C5" s="15" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="D5" s="15" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="6">
@@ -1092,13 +1095,13 @@
         <v>1</v>
       </c>
       <c r="B6" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C6" s="15" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="D6" s="15" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
     </row>
     <row r="7">
@@ -1106,13 +1109,13 @@
         <v>1</v>
       </c>
       <c r="B7" s="15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C7" s="15" t="s">
-        <v>61</v>
+        <v>62</v>
       </c>
       <c r="D7" s="15" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="8">
@@ -1120,13 +1123,13 @@
         <v>1</v>
       </c>
       <c r="B8" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C8" s="15" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D8" s="15" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
     </row>
     <row r="9">
@@ -1134,7 +1137,7 @@
         <v>1</v>
       </c>
       <c r="B9" s="21" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
       <c r="C9" s="21" t="s">
         <v>1</v>
@@ -1148,7 +1151,7 @@
         <v>1</v>
       </c>
       <c r="B10" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C10" s="15" t="s">
         <v>19</v>
@@ -1162,7 +1165,7 @@
         <v>1</v>
       </c>
       <c r="B11" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C11" s="15" t="s">
         <v>20</v>
@@ -1176,7 +1179,7 @@
         <v>1</v>
       </c>
       <c r="B12" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C12" s="15" t="s">
         <v>21</v>
@@ -1190,7 +1193,7 @@
         <v>1</v>
       </c>
       <c r="B13" s="15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C13" s="15" t="s">
         <v>22</v>
@@ -1204,7 +1207,7 @@
         <v>1</v>
       </c>
       <c r="B14" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C14" s="15" t="s">
         <v>23</v>
@@ -1218,7 +1221,7 @@
         <v>1</v>
       </c>
       <c r="B15" s="21" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="C15" s="21" t="s">
         <v>1</v>
@@ -1232,13 +1235,13 @@
         <v>1</v>
       </c>
       <c r="B16" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C16" s="15" t="s">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="D16" s="15" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="17">
@@ -1246,13 +1249,13 @@
         <v>1</v>
       </c>
       <c r="B17" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C17" s="15" t="s">
-        <v>64</v>
+        <v>65</v>
       </c>
       <c r="D17" s="15" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
     </row>
     <row r="18">
@@ -1260,13 +1263,13 @@
         <v>1</v>
       </c>
       <c r="B18" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C18" s="15" t="s">
-        <v>65</v>
+        <v>66</v>
       </c>
       <c r="D18" s="15" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="19">
@@ -1274,13 +1277,13 @@
         <v>1</v>
       </c>
       <c r="B19" s="15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C19" s="15" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="D19" s="15" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
     </row>
     <row r="20">
@@ -1288,13 +1291,13 @@
         <v>1</v>
       </c>
       <c r="B20" s="15" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C20" s="15" t="s">
-        <v>67</v>
+        <v>68</v>
       </c>
       <c r="D20" s="15" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="21">
@@ -1302,7 +1305,7 @@
         <v>1</v>
       </c>
       <c r="B21" s="21" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
       <c r="C21" s="21" t="s">
         <v>1</v>
@@ -1316,13 +1319,13 @@
         <v>1</v>
       </c>
       <c r="B22" s="15" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="C22" s="15" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="D22" s="15" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
     </row>
     <row r="23">
@@ -1330,13 +1333,13 @@
         <v>1</v>
       </c>
       <c r="B23" s="15" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
       <c r="C23" s="15" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="D23" s="15" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="24">
@@ -1344,13 +1347,13 @@
         <v>1</v>
       </c>
       <c r="B24" s="15" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="C24" s="15" t="s">
-        <v>70</v>
+        <v>71</v>
       </c>
       <c r="D24" s="15" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
     </row>
     <row r="25">
@@ -1358,13 +1361,13 @@
         <v>1</v>
       </c>
       <c r="B25" s="15" t="s">
-        <v>53</v>
+        <v>54</v>
       </c>
       <c r="C25" s="15" t="s">
-        <v>71</v>
+        <v>72</v>
       </c>
       <c r="D25" s="15" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="26">
@@ -1372,13 +1375,13 @@
         <v>1</v>
       </c>
       <c r="B26" s="26" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="C26" s="26" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="D26" s="26" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
     </row>
   </sheetData>
